--- a/data/field_polygons.xlsx
+++ b/data/field_polygons.xlsx
@@ -1,15 +1,20 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="4" rupBuild="14420"/>
   <workbookPr defaultThemeVersion="124226"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sibale\Desktop\Flask FarmManagementSystem\data\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
   <bookViews>
     <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="124519"/>
 </workbook>
 </file>
 
@@ -319,8 +324,8 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -383,6 +388,14 @@
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
@@ -429,7 +442,7 @@
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Cambria"/>
+        <a:latin typeface="Cambria" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -461,9 +474,10 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri"/>
+        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -495,6 +509,7 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme name="Office">
@@ -670,11 +685,11 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:F43"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:6">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -694,7 +709,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:6">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>6</v>
       </c>
@@ -714,7 +729,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="3" spans="1:6">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>7</v>
       </c>
@@ -725,7 +740,7 @@
         <v>55</v>
       </c>
       <c r="D3">
-        <v>9.135</v>
+        <v>9.1349999999999998</v>
       </c>
       <c r="E3" t="s">
         <v>58</v>
@@ -734,7 +749,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="4" spans="1:6">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>8</v>
       </c>
@@ -754,7 +769,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="5" spans="1:6">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>9</v>
       </c>
@@ -774,7 +789,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="6" spans="1:6">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>10</v>
       </c>
@@ -785,7 +800,7 @@
         <v>55</v>
       </c>
       <c r="D6">
-        <v>17.124</v>
+        <v>17.123999999999999</v>
       </c>
       <c r="E6" t="s">
         <v>61</v>
@@ -794,7 +809,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="7" spans="1:6">
+    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>11</v>
       </c>
@@ -814,7 +829,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="8" spans="1:6">
+    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>12</v>
       </c>
@@ -825,7 +840,7 @@
         <v>55</v>
       </c>
       <c r="D8">
-        <v>23.658</v>
+        <v>23.658000000000001</v>
       </c>
       <c r="E8" t="s">
         <v>63</v>
@@ -834,7 +849,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="9" spans="1:6">
+    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>13</v>
       </c>
@@ -854,7 +869,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="10" spans="1:6">
+    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>14</v>
       </c>
@@ -874,7 +889,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="11" spans="1:6">
+    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>15</v>
       </c>
@@ -894,7 +909,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="12" spans="1:6">
+    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>16</v>
       </c>
@@ -905,7 +920,7 @@
         <v>55</v>
       </c>
       <c r="D12">
-        <v>10.646</v>
+        <v>10.646000000000001</v>
       </c>
       <c r="E12" t="s">
         <v>67</v>
@@ -914,7 +929,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="13" spans="1:6">
+    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>17</v>
       </c>
@@ -934,7 +949,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="14" spans="1:6">
+    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>18</v>
       </c>
@@ -954,7 +969,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="15" spans="1:6">
+    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>19</v>
       </c>
@@ -965,7 +980,7 @@
         <v>55</v>
       </c>
       <c r="D15">
-        <v>17.504</v>
+        <v>17.504000000000001</v>
       </c>
       <c r="E15" t="s">
         <v>70</v>
@@ -974,7 +989,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="16" spans="1:6">
+    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>20</v>
       </c>
@@ -994,7 +1009,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="17" spans="1:6">
+    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>21</v>
       </c>
@@ -1005,7 +1020,7 @@
         <v>54</v>
       </c>
       <c r="D17">
-        <v>17.328</v>
+        <v>17.327999999999999</v>
       </c>
       <c r="E17" t="s">
         <v>72</v>
@@ -1014,7 +1029,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="18" spans="1:6">
+    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>22</v>
       </c>
@@ -1034,7 +1049,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="19" spans="1:6">
+    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>23</v>
       </c>
@@ -1045,7 +1060,7 @@
         <v>54</v>
       </c>
       <c r="D19">
-        <v>7.174</v>
+        <v>7.1740000000000004</v>
       </c>
       <c r="E19" t="s">
         <v>74</v>
@@ -1054,7 +1069,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="20" spans="1:6">
+    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>24</v>
       </c>
@@ -1074,7 +1089,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="21" spans="1:6">
+    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>25</v>
       </c>
@@ -1094,7 +1109,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="22" spans="1:6">
+    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>26</v>
       </c>
@@ -1105,7 +1120,7 @@
         <v>56</v>
       </c>
       <c r="D22">
-        <v>16.079</v>
+        <v>16.079000000000001</v>
       </c>
       <c r="E22" t="s">
         <v>77</v>
@@ -1114,7 +1129,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="23" spans="1:6">
+    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>27</v>
       </c>
@@ -1125,7 +1140,7 @@
         <v>56</v>
       </c>
       <c r="D23">
-        <v>16.889</v>
+        <v>16.888999999999999</v>
       </c>
       <c r="E23" t="s">
         <v>78</v>
@@ -1134,7 +1149,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="24" spans="1:6">
+    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>28</v>
       </c>
@@ -1154,7 +1169,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="25" spans="1:6">
+    <row r="25" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>29</v>
       </c>
@@ -1165,7 +1180,7 @@
         <v>56</v>
       </c>
       <c r="D25">
-        <v>19.15</v>
+        <v>19.149999999999999</v>
       </c>
       <c r="E25" t="s">
         <v>80</v>
@@ -1174,7 +1189,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="26" spans="1:6">
+    <row r="26" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>30</v>
       </c>
@@ -1185,7 +1200,7 @@
         <v>56</v>
       </c>
       <c r="D26">
-        <v>18.325</v>
+        <v>18.324999999999999</v>
       </c>
       <c r="E26" t="s">
         <v>81</v>
@@ -1194,7 +1209,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="27" spans="1:6">
+    <row r="27" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>31</v>
       </c>
@@ -1214,7 +1229,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="28" spans="1:6">
+    <row r="28" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>32</v>
       </c>
@@ -1225,7 +1240,7 @@
         <v>56</v>
       </c>
       <c r="D28">
-        <v>8.904</v>
+        <v>8.9039999999999999</v>
       </c>
       <c r="E28" t="s">
         <v>83</v>
@@ -1234,7 +1249,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="29" spans="1:6">
+    <row r="29" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>33</v>
       </c>
@@ -1245,7 +1260,7 @@
         <v>56</v>
       </c>
       <c r="D29">
-        <v>21.858</v>
+        <v>21.858000000000001</v>
       </c>
       <c r="E29" t="s">
         <v>84</v>
@@ -1254,7 +1269,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="30" spans="1:6">
+    <row r="30" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
         <v>34</v>
       </c>
@@ -1265,7 +1280,7 @@
         <v>56</v>
       </c>
       <c r="D30">
-        <v>23.162</v>
+        <v>23.161999999999999</v>
       </c>
       <c r="E30" t="s">
         <v>85</v>
@@ -1274,7 +1289,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="31" spans="1:6">
+    <row r="31" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
         <v>35</v>
       </c>
@@ -1285,7 +1300,7 @@
         <v>56</v>
       </c>
       <c r="D31">
-        <v>24.107</v>
+        <v>24.106999999999999</v>
       </c>
       <c r="E31" t="s">
         <v>86</v>
@@ -1294,7 +1309,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="32" spans="1:6">
+    <row r="32" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
         <v>36</v>
       </c>
@@ -1305,7 +1320,7 @@
         <v>56</v>
       </c>
       <c r="D32">
-        <v>25.193</v>
+        <v>25.193000000000001</v>
       </c>
       <c r="E32" t="s">
         <v>87</v>
@@ -1314,7 +1329,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="33" spans="1:6">
+    <row r="33" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
         <v>37</v>
       </c>
@@ -1325,7 +1340,7 @@
         <v>56</v>
       </c>
       <c r="D33">
-        <v>24.804</v>
+        <v>24.803999999999998</v>
       </c>
       <c r="E33" t="s">
         <v>88</v>
@@ -1334,7 +1349,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="34" spans="1:6">
+    <row r="34" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
         <v>38</v>
       </c>
@@ -1345,7 +1360,7 @@
         <v>56</v>
       </c>
       <c r="D34">
-        <v>23.147</v>
+        <v>23.146999999999998</v>
       </c>
       <c r="E34" t="s">
         <v>89</v>
@@ -1354,7 +1369,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="35" spans="1:6">
+    <row r="35" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
         <v>39</v>
       </c>
@@ -1374,7 +1389,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="36" spans="1:6">
+    <row r="36" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
         <v>40</v>
       </c>
@@ -1385,7 +1400,7 @@
         <v>56</v>
       </c>
       <c r="D36">
-        <v>4.195</v>
+        <v>4.1950000000000003</v>
       </c>
       <c r="E36" t="s">
         <v>91</v>
@@ -1394,7 +1409,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="37" spans="1:6">
+    <row r="37" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
         <v>41</v>
       </c>
@@ -1405,7 +1420,7 @@
         <v>56</v>
       </c>
       <c r="D37">
-        <v>8.738</v>
+        <v>8.7379999999999995</v>
       </c>
       <c r="E37" t="s">
         <v>92</v>
@@ -1414,7 +1429,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="38" spans="1:6">
+    <row r="38" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
         <v>42</v>
       </c>
@@ -1425,7 +1440,7 @@
         <v>56</v>
       </c>
       <c r="D38">
-        <v>25.047</v>
+        <v>25.047000000000001</v>
       </c>
       <c r="E38" t="s">
         <v>93</v>
@@ -1434,7 +1449,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="39" spans="1:6">
+    <row r="39" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
         <v>43</v>
       </c>
@@ -1445,7 +1460,7 @@
         <v>56</v>
       </c>
       <c r="D39">
-        <v>21.138</v>
+        <v>21.138000000000002</v>
       </c>
       <c r="E39" t="s">
         <v>94</v>
@@ -1454,7 +1469,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="40" spans="1:6">
+    <row r="40" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
         <v>44</v>
       </c>
@@ -1465,7 +1480,7 @@
         <v>56</v>
       </c>
       <c r="D40">
-        <v>24.543</v>
+        <v>24.542999999999999</v>
       </c>
       <c r="E40" t="s">
         <v>95</v>
@@ -1474,7 +1489,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="41" spans="1:6">
+    <row r="41" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
         <v>45</v>
       </c>
@@ -1485,7 +1500,7 @@
         <v>56</v>
       </c>
       <c r="D41">
-        <v>12.601</v>
+        <v>12.601000000000001</v>
       </c>
       <c r="E41" t="s">
         <v>96</v>
@@ -1494,7 +1509,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="42" spans="1:6">
+    <row r="42" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
         <v>46</v>
       </c>
@@ -1505,7 +1520,7 @@
         <v>54</v>
       </c>
       <c r="D42">
-        <v>9.779999999999999</v>
+        <v>9.7799999999999994</v>
       </c>
       <c r="E42" t="s">
         <v>97</v>
@@ -1514,7 +1529,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="43" spans="1:6">
+    <row r="43" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
         <v>47</v>
       </c>

--- a/data/field_polygons.xlsx
+++ b/data/field_polygons.xlsx
@@ -1,20 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="4" rupBuild="14420"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
   <workbookPr defaultThemeVersion="124226"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sibale\Desktop\Flask FarmManagementSystem\data\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
   <bookViews>
     <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="124519"/>
+  <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
@@ -324,8 +319,8 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="2" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <fonts count="2">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -388,14 +383,6 @@
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
 </styleSheet>
 </file>
 
@@ -442,7 +429,7 @@
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Cambria" panose="020F0302020204030204"/>
+        <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -474,10 +461,9 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+        <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -509,7 +495,6 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme name="Office">
@@ -685,11 +670,11 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:F43"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:6">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -709,7 +694,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:6">
       <c r="A2" t="s">
         <v>6</v>
       </c>
@@ -729,7 +714,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:6">
       <c r="A3" t="s">
         <v>7</v>
       </c>
@@ -740,7 +725,7 @@
         <v>55</v>
       </c>
       <c r="D3">
-        <v>9.1349999999999998</v>
+        <v>9.135</v>
       </c>
       <c r="E3" t="s">
         <v>58</v>
@@ -749,7 +734,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:6">
       <c r="A4" t="s">
         <v>8</v>
       </c>
@@ -769,7 +754,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:6">
       <c r="A5" t="s">
         <v>9</v>
       </c>
@@ -789,7 +774,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:6">
       <c r="A6" t="s">
         <v>10</v>
       </c>
@@ -800,7 +785,7 @@
         <v>55</v>
       </c>
       <c r="D6">
-        <v>17.123999999999999</v>
+        <v>17.124</v>
       </c>
       <c r="E6" t="s">
         <v>61</v>
@@ -809,7 +794,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:6">
       <c r="A7" t="s">
         <v>11</v>
       </c>
@@ -829,7 +814,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:6">
       <c r="A8" t="s">
         <v>12</v>
       </c>
@@ -840,7 +825,7 @@
         <v>55</v>
       </c>
       <c r="D8">
-        <v>23.658000000000001</v>
+        <v>23.658</v>
       </c>
       <c r="E8" t="s">
         <v>63</v>
@@ -849,7 +834,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:6">
       <c r="A9" t="s">
         <v>13</v>
       </c>
@@ -869,7 +854,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:6">
       <c r="A10" t="s">
         <v>14</v>
       </c>
@@ -889,7 +874,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:6">
       <c r="A11" t="s">
         <v>15</v>
       </c>
@@ -909,7 +894,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:6">
       <c r="A12" t="s">
         <v>16</v>
       </c>
@@ -920,7 +905,7 @@
         <v>55</v>
       </c>
       <c r="D12">
-        <v>10.646000000000001</v>
+        <v>10.646</v>
       </c>
       <c r="E12" t="s">
         <v>67</v>
@@ -929,7 +914,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:6">
       <c r="A13" t="s">
         <v>17</v>
       </c>
@@ -949,7 +934,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:6">
       <c r="A14" t="s">
         <v>18</v>
       </c>
@@ -969,7 +954,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:6">
       <c r="A15" t="s">
         <v>19</v>
       </c>
@@ -980,7 +965,7 @@
         <v>55</v>
       </c>
       <c r="D15">
-        <v>17.504000000000001</v>
+        <v>17.504</v>
       </c>
       <c r="E15" t="s">
         <v>70</v>
@@ -989,7 +974,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:6">
       <c r="A16" t="s">
         <v>20</v>
       </c>
@@ -1009,7 +994,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:6">
       <c r="A17" t="s">
         <v>21</v>
       </c>
@@ -1020,7 +1005,7 @@
         <v>54</v>
       </c>
       <c r="D17">
-        <v>17.327999999999999</v>
+        <v>17.328</v>
       </c>
       <c r="E17" t="s">
         <v>72</v>
@@ -1029,7 +1014,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:6">
       <c r="A18" t="s">
         <v>22</v>
       </c>
@@ -1049,7 +1034,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:6">
       <c r="A19" t="s">
         <v>23</v>
       </c>
@@ -1060,7 +1045,7 @@
         <v>54</v>
       </c>
       <c r="D19">
-        <v>7.1740000000000004</v>
+        <v>7.174</v>
       </c>
       <c r="E19" t="s">
         <v>74</v>
@@ -1069,7 +1054,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:6">
       <c r="A20" t="s">
         <v>24</v>
       </c>
@@ -1089,7 +1074,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:6">
       <c r="A21" t="s">
         <v>25</v>
       </c>
@@ -1109,7 +1094,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:6">
       <c r="A22" t="s">
         <v>26</v>
       </c>
@@ -1120,7 +1105,7 @@
         <v>56</v>
       </c>
       <c r="D22">
-        <v>16.079000000000001</v>
+        <v>16.079</v>
       </c>
       <c r="E22" t="s">
         <v>77</v>
@@ -1129,7 +1114,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:6">
       <c r="A23" t="s">
         <v>27</v>
       </c>
@@ -1140,7 +1125,7 @@
         <v>56</v>
       </c>
       <c r="D23">
-        <v>16.888999999999999</v>
+        <v>16.889</v>
       </c>
       <c r="E23" t="s">
         <v>78</v>
@@ -1149,7 +1134,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:6">
       <c r="A24" t="s">
         <v>28</v>
       </c>
@@ -1169,7 +1154,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:6">
       <c r="A25" t="s">
         <v>29</v>
       </c>
@@ -1180,7 +1165,7 @@
         <v>56</v>
       </c>
       <c r="D25">
-        <v>19.149999999999999</v>
+        <v>19.15</v>
       </c>
       <c r="E25" t="s">
         <v>80</v>
@@ -1189,7 +1174,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:6">
       <c r="A26" t="s">
         <v>30</v>
       </c>
@@ -1200,7 +1185,7 @@
         <v>56</v>
       </c>
       <c r="D26">
-        <v>18.324999999999999</v>
+        <v>18.325</v>
       </c>
       <c r="E26" t="s">
         <v>81</v>
@@ -1209,7 +1194,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="27" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:6">
       <c r="A27" t="s">
         <v>31</v>
       </c>
@@ -1229,7 +1214,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="28" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:6">
       <c r="A28" t="s">
         <v>32</v>
       </c>
@@ -1240,7 +1225,7 @@
         <v>56</v>
       </c>
       <c r="D28">
-        <v>8.9039999999999999</v>
+        <v>8.904</v>
       </c>
       <c r="E28" t="s">
         <v>83</v>
@@ -1249,7 +1234,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="29" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:6">
       <c r="A29" t="s">
         <v>33</v>
       </c>
@@ -1260,7 +1245,7 @@
         <v>56</v>
       </c>
       <c r="D29">
-        <v>21.858000000000001</v>
+        <v>21.858</v>
       </c>
       <c r="E29" t="s">
         <v>84</v>
@@ -1269,7 +1254,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="30" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:6">
       <c r="A30" t="s">
         <v>34</v>
       </c>
@@ -1280,7 +1265,7 @@
         <v>56</v>
       </c>
       <c r="D30">
-        <v>23.161999999999999</v>
+        <v>23.162</v>
       </c>
       <c r="E30" t="s">
         <v>85</v>
@@ -1289,7 +1274,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="31" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:6">
       <c r="A31" t="s">
         <v>35</v>
       </c>
@@ -1300,7 +1285,7 @@
         <v>56</v>
       </c>
       <c r="D31">
-        <v>24.106999999999999</v>
+        <v>24.107</v>
       </c>
       <c r="E31" t="s">
         <v>86</v>
@@ -1309,7 +1294,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="32" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:6">
       <c r="A32" t="s">
         <v>36</v>
       </c>
@@ -1320,7 +1305,7 @@
         <v>56</v>
       </c>
       <c r="D32">
-        <v>25.193000000000001</v>
+        <v>25.193</v>
       </c>
       <c r="E32" t="s">
         <v>87</v>
@@ -1329,7 +1314,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="33" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:6">
       <c r="A33" t="s">
         <v>37</v>
       </c>
@@ -1340,7 +1325,7 @@
         <v>56</v>
       </c>
       <c r="D33">
-        <v>24.803999999999998</v>
+        <v>24.804</v>
       </c>
       <c r="E33" t="s">
         <v>88</v>
@@ -1349,7 +1334,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="34" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:6">
       <c r="A34" t="s">
         <v>38</v>
       </c>
@@ -1360,7 +1345,7 @@
         <v>56</v>
       </c>
       <c r="D34">
-        <v>23.146999999999998</v>
+        <v>23.147</v>
       </c>
       <c r="E34" t="s">
         <v>89</v>
@@ -1369,7 +1354,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="35" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:6">
       <c r="A35" t="s">
         <v>39</v>
       </c>
@@ -1389,7 +1374,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="36" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:6">
       <c r="A36" t="s">
         <v>40</v>
       </c>
@@ -1400,7 +1385,7 @@
         <v>56</v>
       </c>
       <c r="D36">
-        <v>4.1950000000000003</v>
+        <v>4.195</v>
       </c>
       <c r="E36" t="s">
         <v>91</v>
@@ -1409,7 +1394,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="37" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:6">
       <c r="A37" t="s">
         <v>41</v>
       </c>
@@ -1420,7 +1405,7 @@
         <v>56</v>
       </c>
       <c r="D37">
-        <v>8.7379999999999995</v>
+        <v>8.738</v>
       </c>
       <c r="E37" t="s">
         <v>92</v>
@@ -1429,7 +1414,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="38" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:6">
       <c r="A38" t="s">
         <v>42</v>
       </c>
@@ -1440,7 +1425,7 @@
         <v>56</v>
       </c>
       <c r="D38">
-        <v>25.047000000000001</v>
+        <v>25.047</v>
       </c>
       <c r="E38" t="s">
         <v>93</v>
@@ -1449,7 +1434,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="39" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:6">
       <c r="A39" t="s">
         <v>43</v>
       </c>
@@ -1460,7 +1445,7 @@
         <v>56</v>
       </c>
       <c r="D39">
-        <v>21.138000000000002</v>
+        <v>21.138</v>
       </c>
       <c r="E39" t="s">
         <v>94</v>
@@ -1469,7 +1454,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="40" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:6">
       <c r="A40" t="s">
         <v>44</v>
       </c>
@@ -1480,7 +1465,7 @@
         <v>56</v>
       </c>
       <c r="D40">
-        <v>24.542999999999999</v>
+        <v>24.543</v>
       </c>
       <c r="E40" t="s">
         <v>95</v>
@@ -1489,7 +1474,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="41" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:6">
       <c r="A41" t="s">
         <v>45</v>
       </c>
@@ -1500,7 +1485,7 @@
         <v>56</v>
       </c>
       <c r="D41">
-        <v>12.601000000000001</v>
+        <v>12.601</v>
       </c>
       <c r="E41" t="s">
         <v>96</v>
@@ -1509,7 +1494,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="42" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:6">
       <c r="A42" t="s">
         <v>46</v>
       </c>
@@ -1520,7 +1505,7 @@
         <v>54</v>
       </c>
       <c r="D42">
-        <v>9.7799999999999994</v>
+        <v>9.779999999999999</v>
       </c>
       <c r="E42" t="s">
         <v>97</v>
@@ -1529,7 +1514,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="43" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:6">
       <c r="A43" t="s">
         <v>47</v>
       </c>

--- a/data/field_polygons.xlsx
+++ b/data/field_polygons.xlsx
@@ -14,9 +14,9 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="216" uniqueCount="100">
-  <si>
-    <t>Field Name</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="216" uniqueCount="102">
+  <si>
+    <t>Field</t>
   </si>
   <si>
     <t>Crop</t>
@@ -311,6 +311,12 @@
   </si>
   <si>
     <t>{"type": "FeatureCollection", "features": [{"type": "Feature", "properties": {}, "geometry": {"type": "Polygon", "coordinates": [[[34.150497, -12.555148], [34.148115, -12.556498], [34.148689, -12.557086], [34.14952, -12.557955], [34.150454, -12.558865], [34.150556, -12.558892], [34.150743, -12.558682], [34.151672, -12.558169], [34.152605, -12.557698], [34.15297, -12.557536], [34.151757, -12.556332], [34.150497, -12.555148]]]}}]}</t>
+  </si>
+  <si>
+    <t>Critical</t>
+  </si>
+  <si>
+    <t>Moderate</t>
   </si>
   <si>
     <t>Low</t>
@@ -811,7 +817,7 @@
         <v>62</v>
       </c>
       <c r="F7" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
     </row>
     <row r="8" spans="1:6">
@@ -991,7 +997,7 @@
         <v>71</v>
       </c>
       <c r="F16" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
     </row>
     <row r="17" spans="1:6">
@@ -1011,7 +1017,7 @@
         <v>72</v>
       </c>
       <c r="F17" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
     </row>
     <row r="18" spans="1:6">
@@ -1031,7 +1037,7 @@
         <v>73</v>
       </c>
       <c r="F18" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
     </row>
     <row r="19" spans="1:6">

--- a/data/field_polygons.xlsx
+++ b/data/field_polygons.xlsx
@@ -313,10 +313,10 @@
     <t>{"type": "FeatureCollection", "features": [{"type": "Feature", "properties": {}, "geometry": {"type": "Polygon", "coordinates": [[[34.150497, -12.555148], [34.148115, -12.556498], [34.148689, -12.557086], [34.14952, -12.557955], [34.150454, -12.558865], [34.150556, -12.558892], [34.150743, -12.558682], [34.151672, -12.558169], [34.152605, -12.557698], [34.15297, -12.557536], [34.151757, -12.556332], [34.150497, -12.555148]]]}}]}</t>
   </si>
   <si>
+    <t>Moderate</t>
+  </si>
+  <si>
     <t>Critical</t>
-  </si>
-  <si>
-    <t>Moderate</t>
   </si>
   <si>
     <t>Low</t>
@@ -737,7 +737,7 @@
         <v>58</v>
       </c>
       <c r="F3" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
     </row>
     <row r="4" spans="1:6">
@@ -757,7 +757,7 @@
         <v>59</v>
       </c>
       <c r="F4" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
     </row>
     <row r="5" spans="1:6">
@@ -777,7 +777,7 @@
         <v>60</v>
       </c>
       <c r="F5" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
     </row>
     <row r="6" spans="1:6">
@@ -797,7 +797,7 @@
         <v>61</v>
       </c>
       <c r="F6" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
     </row>
     <row r="7" spans="1:6">
@@ -817,7 +817,7 @@
         <v>62</v>
       </c>
       <c r="F7" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
     </row>
     <row r="8" spans="1:6">
@@ -837,7 +837,7 @@
         <v>63</v>
       </c>
       <c r="F8" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
     </row>
     <row r="9" spans="1:6">
@@ -857,7 +857,7 @@
         <v>64</v>
       </c>
       <c r="F9" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
     </row>
     <row r="10" spans="1:6">
@@ -877,7 +877,7 @@
         <v>65</v>
       </c>
       <c r="F10" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
     </row>
     <row r="11" spans="1:6">
@@ -897,7 +897,7 @@
         <v>66</v>
       </c>
       <c r="F11" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
     </row>
     <row r="12" spans="1:6">
@@ -917,7 +917,7 @@
         <v>67</v>
       </c>
       <c r="F12" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
     </row>
     <row r="13" spans="1:6">
@@ -937,7 +937,7 @@
         <v>68</v>
       </c>
       <c r="F13" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
     </row>
     <row r="14" spans="1:6">
@@ -957,7 +957,7 @@
         <v>69</v>
       </c>
       <c r="F14" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
     </row>
     <row r="15" spans="1:6">
@@ -977,7 +977,7 @@
         <v>70</v>
       </c>
       <c r="F15" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
     </row>
     <row r="16" spans="1:6">
@@ -997,7 +997,7 @@
         <v>71</v>
       </c>
       <c r="F16" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
     </row>
     <row r="17" spans="1:6">
@@ -1057,7 +1057,7 @@
         <v>74</v>
       </c>
       <c r="F19" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
     </row>
     <row r="20" spans="1:6">
@@ -1077,7 +1077,7 @@
         <v>75</v>
       </c>
       <c r="F20" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
     </row>
     <row r="21" spans="1:6">
@@ -1097,7 +1097,7 @@
         <v>76</v>
       </c>
       <c r="F21" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
     </row>
     <row r="22" spans="1:6">
@@ -1117,7 +1117,7 @@
         <v>77</v>
       </c>
       <c r="F22" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
     </row>
     <row r="23" spans="1:6">
@@ -1137,7 +1137,7 @@
         <v>78</v>
       </c>
       <c r="F23" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
     </row>
     <row r="24" spans="1:6">
@@ -1157,7 +1157,7 @@
         <v>79</v>
       </c>
       <c r="F24" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
     </row>
     <row r="25" spans="1:6">
@@ -1177,7 +1177,7 @@
         <v>80</v>
       </c>
       <c r="F25" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
     </row>
     <row r="26" spans="1:6">
@@ -1197,7 +1197,7 @@
         <v>81</v>
       </c>
       <c r="F26" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
     </row>
     <row r="27" spans="1:6">
@@ -1217,7 +1217,7 @@
         <v>82</v>
       </c>
       <c r="F27" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
     </row>
     <row r="28" spans="1:6">
@@ -1237,7 +1237,7 @@
         <v>83</v>
       </c>
       <c r="F28" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
     </row>
     <row r="29" spans="1:6">
@@ -1257,7 +1257,7 @@
         <v>84</v>
       </c>
       <c r="F29" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
     </row>
     <row r="30" spans="1:6">
@@ -1277,7 +1277,7 @@
         <v>85</v>
       </c>
       <c r="F30" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
     </row>
     <row r="31" spans="1:6">
@@ -1297,7 +1297,7 @@
         <v>86</v>
       </c>
       <c r="F31" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
     </row>
     <row r="32" spans="1:6">
@@ -1317,7 +1317,7 @@
         <v>87</v>
       </c>
       <c r="F32" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
     </row>
     <row r="33" spans="1:6">
@@ -1337,7 +1337,7 @@
         <v>88</v>
       </c>
       <c r="F33" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
     </row>
     <row r="34" spans="1:6">
@@ -1357,7 +1357,7 @@
         <v>89</v>
       </c>
       <c r="F34" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
     </row>
     <row r="35" spans="1:6">
@@ -1377,7 +1377,7 @@
         <v>90</v>
       </c>
       <c r="F35" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
     </row>
     <row r="36" spans="1:6">
@@ -1397,7 +1397,7 @@
         <v>91</v>
       </c>
       <c r="F36" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
     </row>
     <row r="37" spans="1:6">
@@ -1417,7 +1417,7 @@
         <v>92</v>
       </c>
       <c r="F37" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
     </row>
     <row r="38" spans="1:6">
@@ -1437,7 +1437,7 @@
         <v>93</v>
       </c>
       <c r="F38" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
     </row>
     <row r="39" spans="1:6">
@@ -1457,7 +1457,7 @@
         <v>94</v>
       </c>
       <c r="F39" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
     </row>
     <row r="40" spans="1:6">
@@ -1477,7 +1477,7 @@
         <v>95</v>
       </c>
       <c r="F40" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
     </row>
     <row r="41" spans="1:6">
@@ -1497,7 +1497,7 @@
         <v>96</v>
       </c>
       <c r="F41" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
     </row>
     <row r="42" spans="1:6">
@@ -1517,7 +1517,7 @@
         <v>97</v>
       </c>
       <c r="F42" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
     </row>
     <row r="43" spans="1:6">
@@ -1537,7 +1537,7 @@
         <v>98</v>
       </c>
       <c r="F43" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
     </row>
   </sheetData>

--- a/data/field_polygons.xlsx
+++ b/data/field_polygons.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="216" uniqueCount="102">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="216" uniqueCount="100">
   <si>
     <t>Field</t>
   </si>
@@ -311,12 +311,6 @@
   </si>
   <si>
     <t>{"type": "FeatureCollection", "features": [{"type": "Feature", "properties": {}, "geometry": {"type": "Polygon", "coordinates": [[[34.150497, -12.555148], [34.148115, -12.556498], [34.148689, -12.557086], [34.14952, -12.557955], [34.150454, -12.558865], [34.150556, -12.558892], [34.150743, -12.558682], [34.151672, -12.558169], [34.152605, -12.557698], [34.15297, -12.557536], [34.151757, -12.556332], [34.150497, -12.555148]]]}}]}</t>
-  </si>
-  <si>
-    <t>Moderate</t>
-  </si>
-  <si>
-    <t>Critical</t>
   </si>
   <si>
     <t>Low</t>
@@ -737,7 +731,7 @@
         <v>58</v>
       </c>
       <c r="F3" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
     </row>
     <row r="4" spans="1:6">
@@ -757,7 +751,7 @@
         <v>59</v>
       </c>
       <c r="F4" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
     </row>
     <row r="5" spans="1:6">
@@ -777,7 +771,7 @@
         <v>60</v>
       </c>
       <c r="F5" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
     </row>
     <row r="6" spans="1:6">
@@ -797,7 +791,7 @@
         <v>61</v>
       </c>
       <c r="F6" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
     </row>
     <row r="7" spans="1:6">
@@ -837,7 +831,7 @@
         <v>63</v>
       </c>
       <c r="F8" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
     </row>
     <row r="9" spans="1:6">
@@ -857,7 +851,7 @@
         <v>64</v>
       </c>
       <c r="F9" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
     </row>
     <row r="10" spans="1:6">
@@ -877,7 +871,7 @@
         <v>65</v>
       </c>
       <c r="F10" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
     </row>
     <row r="11" spans="1:6">
@@ -897,7 +891,7 @@
         <v>66</v>
       </c>
       <c r="F11" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
     </row>
     <row r="12" spans="1:6">
@@ -917,7 +911,7 @@
         <v>67</v>
       </c>
       <c r="F12" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
     </row>
     <row r="13" spans="1:6">
@@ -937,7 +931,7 @@
         <v>68</v>
       </c>
       <c r="F13" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
     </row>
     <row r="14" spans="1:6">
@@ -957,7 +951,7 @@
         <v>69</v>
       </c>
       <c r="F14" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
     </row>
     <row r="15" spans="1:6">
@@ -977,7 +971,7 @@
         <v>70</v>
       </c>
       <c r="F15" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
     </row>
     <row r="16" spans="1:6">
@@ -1017,7 +1011,7 @@
         <v>72</v>
       </c>
       <c r="F17" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
     </row>
     <row r="18" spans="1:6">
@@ -1037,7 +1031,7 @@
         <v>73</v>
       </c>
       <c r="F18" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
     </row>
     <row r="19" spans="1:6">
@@ -1057,7 +1051,7 @@
         <v>74</v>
       </c>
       <c r="F19" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
     </row>
     <row r="20" spans="1:6">
@@ -1077,7 +1071,7 @@
         <v>75</v>
       </c>
       <c r="F20" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
     </row>
     <row r="21" spans="1:6">
@@ -1097,7 +1091,7 @@
         <v>76</v>
       </c>
       <c r="F21" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
     </row>
     <row r="22" spans="1:6">
@@ -1117,7 +1111,7 @@
         <v>77</v>
       </c>
       <c r="F22" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
     </row>
     <row r="23" spans="1:6">
@@ -1137,7 +1131,7 @@
         <v>78</v>
       </c>
       <c r="F23" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
     </row>
     <row r="24" spans="1:6">
@@ -1157,7 +1151,7 @@
         <v>79</v>
       </c>
       <c r="F24" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
     </row>
     <row r="25" spans="1:6">
@@ -1177,7 +1171,7 @@
         <v>80</v>
       </c>
       <c r="F25" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
     </row>
     <row r="26" spans="1:6">
@@ -1197,7 +1191,7 @@
         <v>81</v>
       </c>
       <c r="F26" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
     </row>
     <row r="27" spans="1:6">
@@ -1217,7 +1211,7 @@
         <v>82</v>
       </c>
       <c r="F27" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
     </row>
     <row r="28" spans="1:6">
@@ -1237,7 +1231,7 @@
         <v>83</v>
       </c>
       <c r="F28" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
     </row>
     <row r="29" spans="1:6">
@@ -1257,7 +1251,7 @@
         <v>84</v>
       </c>
       <c r="F29" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
     </row>
     <row r="30" spans="1:6">
@@ -1277,7 +1271,7 @@
         <v>85</v>
       </c>
       <c r="F30" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
     </row>
     <row r="31" spans="1:6">
@@ -1297,7 +1291,7 @@
         <v>86</v>
       </c>
       <c r="F31" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
     </row>
     <row r="32" spans="1:6">
@@ -1317,7 +1311,7 @@
         <v>87</v>
       </c>
       <c r="F32" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
     </row>
     <row r="33" spans="1:6">
@@ -1337,7 +1331,7 @@
         <v>88</v>
       </c>
       <c r="F33" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
     </row>
     <row r="34" spans="1:6">
@@ -1357,7 +1351,7 @@
         <v>89</v>
       </c>
       <c r="F34" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
     </row>
     <row r="35" spans="1:6">
@@ -1377,7 +1371,7 @@
         <v>90</v>
       </c>
       <c r="F35" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
     </row>
     <row r="36" spans="1:6">
@@ -1397,7 +1391,7 @@
         <v>91</v>
       </c>
       <c r="F36" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
     </row>
     <row r="37" spans="1:6">
@@ -1417,7 +1411,7 @@
         <v>92</v>
       </c>
       <c r="F37" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
     </row>
     <row r="38" spans="1:6">
@@ -1437,7 +1431,7 @@
         <v>93</v>
       </c>
       <c r="F38" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
     </row>
     <row r="39" spans="1:6">
@@ -1457,7 +1451,7 @@
         <v>94</v>
       </c>
       <c r="F39" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
     </row>
     <row r="40" spans="1:6">
@@ -1477,7 +1471,7 @@
         <v>95</v>
       </c>
       <c r="F40" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
     </row>
     <row r="41" spans="1:6">
@@ -1497,7 +1491,7 @@
         <v>96</v>
       </c>
       <c r="F41" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
     </row>
     <row r="42" spans="1:6">
@@ -1517,7 +1511,7 @@
         <v>97</v>
       </c>
       <c r="F42" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
     </row>
     <row r="43" spans="1:6">
@@ -1537,7 +1531,7 @@
         <v>98</v>
       </c>
       <c r="F43" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
     </row>
   </sheetData>

--- a/data/field_polygons.xlsx
+++ b/data/field_polygons.xlsx
@@ -313,7 +313,7 @@
     <t>{"type": "FeatureCollection", "features": [{"type": "Feature", "properties": {}, "geometry": {"type": "Polygon", "coordinates": [[[34.150497, -12.555148], [34.148115, -12.556498], [34.148689, -12.557086], [34.14952, -12.557955], [34.150454, -12.558865], [34.150556, -12.558892], [34.150743, -12.558682], [34.151672, -12.558169], [34.152605, -12.557698], [34.15297, -12.557536], [34.151757, -12.556332], [34.150497, -12.555148]]]}}]}</t>
   </si>
   <si>
-    <t>Low</t>
+    <t>Critical</t>
   </si>
 </sst>
 </file>

--- a/data/field_polygons.xlsx
+++ b/data/field_polygons.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="216" uniqueCount="100">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="216" uniqueCount="102">
   <si>
     <t>Field</t>
   </si>
@@ -311,6 +311,12 @@
   </si>
   <si>
     <t>{"type": "FeatureCollection", "features": [{"type": "Feature", "properties": {}, "geometry": {"type": "Polygon", "coordinates": [[[34.150497, -12.555148], [34.148115, -12.556498], [34.148689, -12.557086], [34.14952, -12.557955], [34.150454, -12.558865], [34.150556, -12.558892], [34.150743, -12.558682], [34.151672, -12.558169], [34.152605, -12.557698], [34.15297, -12.557536], [34.151757, -12.556332], [34.150497, -12.555148]]]}}]}</t>
+  </si>
+  <si>
+    <t>Low</t>
+  </si>
+  <si>
+    <t>High</t>
   </si>
   <si>
     <t>Critical</t>
@@ -731,7 +737,7 @@
         <v>58</v>
       </c>
       <c r="F3" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
     </row>
     <row r="4" spans="1:6">
@@ -751,7 +757,7 @@
         <v>59</v>
       </c>
       <c r="F4" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
     </row>
     <row r="5" spans="1:6">
@@ -771,7 +777,7 @@
         <v>60</v>
       </c>
       <c r="F5" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
     </row>
     <row r="6" spans="1:6">
@@ -791,7 +797,7 @@
         <v>61</v>
       </c>
       <c r="F6" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
     </row>
     <row r="7" spans="1:6">
@@ -811,7 +817,7 @@
         <v>62</v>
       </c>
       <c r="F7" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
     </row>
     <row r="8" spans="1:6">
@@ -851,7 +857,7 @@
         <v>64</v>
       </c>
       <c r="F9" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
     </row>
     <row r="10" spans="1:6">
@@ -871,7 +877,7 @@
         <v>65</v>
       </c>
       <c r="F10" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
     </row>
     <row r="11" spans="1:6">
@@ -891,7 +897,7 @@
         <v>66</v>
       </c>
       <c r="F11" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
     </row>
     <row r="12" spans="1:6">
@@ -911,7 +917,7 @@
         <v>67</v>
       </c>
       <c r="F12" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
     </row>
     <row r="13" spans="1:6">
@@ -931,7 +937,7 @@
         <v>68</v>
       </c>
       <c r="F13" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
     </row>
     <row r="14" spans="1:6">
@@ -951,7 +957,7 @@
         <v>69</v>
       </c>
       <c r="F14" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
     </row>
     <row r="15" spans="1:6">
@@ -971,7 +977,7 @@
         <v>70</v>
       </c>
       <c r="F15" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
     </row>
     <row r="16" spans="1:6">
@@ -991,7 +997,7 @@
         <v>71</v>
       </c>
       <c r="F16" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
     </row>
     <row r="17" spans="1:6">
@@ -1051,7 +1057,7 @@
         <v>74</v>
       </c>
       <c r="F19" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
     </row>
     <row r="20" spans="1:6">
@@ -1071,7 +1077,7 @@
         <v>75</v>
       </c>
       <c r="F20" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
     </row>
     <row r="21" spans="1:6">
@@ -1091,7 +1097,7 @@
         <v>76</v>
       </c>
       <c r="F21" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
     </row>
     <row r="22" spans="1:6">
@@ -1111,7 +1117,7 @@
         <v>77</v>
       </c>
       <c r="F22" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
     </row>
     <row r="23" spans="1:6">
@@ -1131,7 +1137,7 @@
         <v>78</v>
       </c>
       <c r="F23" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
     </row>
     <row r="24" spans="1:6">
@@ -1171,7 +1177,7 @@
         <v>80</v>
       </c>
       <c r="F25" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
     </row>
     <row r="26" spans="1:6">
@@ -1191,7 +1197,7 @@
         <v>81</v>
       </c>
       <c r="F26" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
     </row>
     <row r="27" spans="1:6">
@@ -1211,7 +1217,7 @@
         <v>82</v>
       </c>
       <c r="F27" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
     </row>
     <row r="28" spans="1:6">
@@ -1231,7 +1237,7 @@
         <v>83</v>
       </c>
       <c r="F28" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
     </row>
     <row r="29" spans="1:6">
@@ -1251,7 +1257,7 @@
         <v>84</v>
       </c>
       <c r="F29" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
     </row>
     <row r="30" spans="1:6">
@@ -1271,7 +1277,7 @@
         <v>85</v>
       </c>
       <c r="F30" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
     </row>
     <row r="31" spans="1:6">
@@ -1291,7 +1297,7 @@
         <v>86</v>
       </c>
       <c r="F31" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
     </row>
     <row r="32" spans="1:6">
@@ -1311,7 +1317,7 @@
         <v>87</v>
       </c>
       <c r="F32" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
     </row>
     <row r="33" spans="1:6">
@@ -1331,7 +1337,7 @@
         <v>88</v>
       </c>
       <c r="F33" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
     </row>
     <row r="34" spans="1:6">
@@ -1351,7 +1357,7 @@
         <v>89</v>
       </c>
       <c r="F34" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
     </row>
     <row r="35" spans="1:6">
@@ -1371,7 +1377,7 @@
         <v>90</v>
       </c>
       <c r="F35" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
     </row>
     <row r="36" spans="1:6">
@@ -1411,7 +1417,7 @@
         <v>92</v>
       </c>
       <c r="F37" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
     </row>
     <row r="38" spans="1:6">
@@ -1431,7 +1437,7 @@
         <v>93</v>
       </c>
       <c r="F38" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
     </row>
     <row r="39" spans="1:6">
@@ -1451,7 +1457,7 @@
         <v>94</v>
       </c>
       <c r="F39" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
     </row>
     <row r="40" spans="1:6">
@@ -1471,7 +1477,7 @@
         <v>95</v>
       </c>
       <c r="F40" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
     </row>
     <row r="41" spans="1:6">
@@ -1491,7 +1497,7 @@
         <v>96</v>
       </c>
       <c r="F41" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
     </row>
     <row r="42" spans="1:6">
@@ -1511,7 +1517,7 @@
         <v>97</v>
       </c>
       <c r="F42" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
     </row>
     <row r="43" spans="1:6">
@@ -1531,7 +1537,7 @@
         <v>98</v>
       </c>
       <c r="F43" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
     </row>
   </sheetData>

--- a/data/field_polygons.xlsx
+++ b/data/field_polygons.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="216" uniqueCount="102">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="216" uniqueCount="100">
   <si>
     <t>Field</t>
   </si>
@@ -311,12 +311,6 @@
   </si>
   <si>
     <t>{"type": "FeatureCollection", "features": [{"type": "Feature", "properties": {}, "geometry": {"type": "Polygon", "coordinates": [[[34.150497, -12.555148], [34.148115, -12.556498], [34.148689, -12.557086], [34.14952, -12.557955], [34.150454, -12.558865], [34.150556, -12.558892], [34.150743, -12.558682], [34.151672, -12.558169], [34.152605, -12.557698], [34.15297, -12.557536], [34.151757, -12.556332], [34.150497, -12.555148]]]}}]}</t>
-  </si>
-  <si>
-    <t>Low</t>
-  </si>
-  <si>
-    <t>High</t>
   </si>
   <si>
     <t>Critical</t>
@@ -737,7 +731,7 @@
         <v>58</v>
       </c>
       <c r="F3" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
     </row>
     <row r="4" spans="1:6">
@@ -757,7 +751,7 @@
         <v>59</v>
       </c>
       <c r="F4" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
     </row>
     <row r="5" spans="1:6">
@@ -777,7 +771,7 @@
         <v>60</v>
       </c>
       <c r="F5" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
     </row>
     <row r="6" spans="1:6">
@@ -797,7 +791,7 @@
         <v>61</v>
       </c>
       <c r="F6" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
     </row>
     <row r="7" spans="1:6">
@@ -817,7 +811,7 @@
         <v>62</v>
       </c>
       <c r="F7" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
     </row>
     <row r="8" spans="1:6">
@@ -857,7 +851,7 @@
         <v>64</v>
       </c>
       <c r="F9" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
     </row>
     <row r="10" spans="1:6">
@@ -877,7 +871,7 @@
         <v>65</v>
       </c>
       <c r="F10" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
     </row>
     <row r="11" spans="1:6">
@@ -897,7 +891,7 @@
         <v>66</v>
       </c>
       <c r="F11" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
     </row>
     <row r="12" spans="1:6">
@@ -917,7 +911,7 @@
         <v>67</v>
       </c>
       <c r="F12" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
     </row>
     <row r="13" spans="1:6">
@@ -937,7 +931,7 @@
         <v>68</v>
       </c>
       <c r="F13" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
     </row>
     <row r="14" spans="1:6">
@@ -957,7 +951,7 @@
         <v>69</v>
       </c>
       <c r="F14" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
     </row>
     <row r="15" spans="1:6">
@@ -977,7 +971,7 @@
         <v>70</v>
       </c>
       <c r="F15" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
     </row>
     <row r="16" spans="1:6">
@@ -997,7 +991,7 @@
         <v>71</v>
       </c>
       <c r="F16" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
     </row>
     <row r="17" spans="1:6">
@@ -1057,7 +1051,7 @@
         <v>74</v>
       </c>
       <c r="F19" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
     </row>
     <row r="20" spans="1:6">
@@ -1077,7 +1071,7 @@
         <v>75</v>
       </c>
       <c r="F20" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
     </row>
     <row r="21" spans="1:6">
@@ -1097,7 +1091,7 @@
         <v>76</v>
       </c>
       <c r="F21" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
     </row>
     <row r="22" spans="1:6">
@@ -1117,7 +1111,7 @@
         <v>77</v>
       </c>
       <c r="F22" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
     </row>
     <row r="23" spans="1:6">
@@ -1137,7 +1131,7 @@
         <v>78</v>
       </c>
       <c r="F23" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
     </row>
     <row r="24" spans="1:6">
@@ -1177,7 +1171,7 @@
         <v>80</v>
       </c>
       <c r="F25" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
     </row>
     <row r="26" spans="1:6">
@@ -1197,7 +1191,7 @@
         <v>81</v>
       </c>
       <c r="F26" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
     </row>
     <row r="27" spans="1:6">
@@ -1217,7 +1211,7 @@
         <v>82</v>
       </c>
       <c r="F27" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
     </row>
     <row r="28" spans="1:6">
@@ -1237,7 +1231,7 @@
         <v>83</v>
       </c>
       <c r="F28" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
     </row>
     <row r="29" spans="1:6">
@@ -1257,7 +1251,7 @@
         <v>84</v>
       </c>
       <c r="F29" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
     </row>
     <row r="30" spans="1:6">
@@ -1277,7 +1271,7 @@
         <v>85</v>
       </c>
       <c r="F30" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
     </row>
     <row r="31" spans="1:6">
@@ -1297,7 +1291,7 @@
         <v>86</v>
       </c>
       <c r="F31" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
     </row>
     <row r="32" spans="1:6">
@@ -1317,7 +1311,7 @@
         <v>87</v>
       </c>
       <c r="F32" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
     </row>
     <row r="33" spans="1:6">
@@ -1337,7 +1331,7 @@
         <v>88</v>
       </c>
       <c r="F33" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
     </row>
     <row r="34" spans="1:6">
@@ -1357,7 +1351,7 @@
         <v>89</v>
       </c>
       <c r="F34" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
     </row>
     <row r="35" spans="1:6">
@@ -1377,7 +1371,7 @@
         <v>90</v>
       </c>
       <c r="F35" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
     </row>
     <row r="36" spans="1:6">
@@ -1417,7 +1411,7 @@
         <v>92</v>
       </c>
       <c r="F37" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
     </row>
     <row r="38" spans="1:6">
@@ -1437,7 +1431,7 @@
         <v>93</v>
       </c>
       <c r="F38" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
     </row>
     <row r="39" spans="1:6">
@@ -1457,7 +1451,7 @@
         <v>94</v>
       </c>
       <c r="F39" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
     </row>
     <row r="40" spans="1:6">
@@ -1477,7 +1471,7 @@
         <v>95</v>
       </c>
       <c r="F40" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
     </row>
     <row r="41" spans="1:6">
@@ -1497,7 +1491,7 @@
         <v>96</v>
       </c>
       <c r="F41" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
     </row>
     <row r="42" spans="1:6">
@@ -1517,7 +1511,7 @@
         <v>97</v>
       </c>
       <c r="F42" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
     </row>
     <row r="43" spans="1:6">
@@ -1537,7 +1531,7 @@
         <v>98</v>
       </c>
       <c r="F43" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
     </row>
   </sheetData>

--- a/data/field_polygons.xlsx
+++ b/data/field_polygons.xlsx
@@ -313,7 +313,7 @@
     <t>{"type": "FeatureCollection", "features": [{"type": "Feature", "properties": {}, "geometry": {"type": "Polygon", "coordinates": [[[34.150497, -12.555148], [34.148115, -12.556498], [34.148689, -12.557086], [34.14952, -12.557955], [34.150454, -12.558865], [34.150556, -12.558892], [34.150743, -12.558682], [34.151672, -12.558169], [34.152605, -12.557698], [34.15297, -12.557536], [34.151757, -12.556332], [34.150497, -12.555148]]]}}]}</t>
   </si>
   <si>
-    <t>Critical</t>
+    <t>Low</t>
   </si>
 </sst>
 </file>

--- a/data/field_polygons.xlsx
+++ b/data/field_polygons.xlsx
@@ -1,15 +1,20 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="4" rupBuild="14420"/>
   <workbookPr defaultThemeVersion="124226"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sibale\Desktop\Flask FarmManagementSystem\data\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
   <bookViews>
     <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="162913"/>
 </workbook>
 </file>
 
@@ -319,8 +324,8 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -383,6 +388,14 @@
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
@@ -429,7 +442,7 @@
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Cambria"/>
+        <a:latin typeface="Cambria" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -461,9 +474,10 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri"/>
+        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -495,6 +509,7 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme name="Office">
@@ -670,11 +685,11 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:F43"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:6">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -694,7 +709,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:6">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>6</v>
       </c>
@@ -714,7 +729,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="3" spans="1:6">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>7</v>
       </c>
@@ -725,7 +740,7 @@
         <v>55</v>
       </c>
       <c r="D3">
-        <v>9.135</v>
+        <v>9.1349999999999998</v>
       </c>
       <c r="E3" t="s">
         <v>58</v>
@@ -734,7 +749,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="4" spans="1:6">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>8</v>
       </c>
@@ -745,7 +760,7 @@
         <v>55</v>
       </c>
       <c r="D4">
-        <v>10.141</v>
+        <v>16.341999999999999</v>
       </c>
       <c r="E4" t="s">
         <v>59</v>
@@ -754,7 +769,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="5" spans="1:6">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>9</v>
       </c>
@@ -765,7 +780,7 @@
         <v>55</v>
       </c>
       <c r="D5">
-        <v>15.439</v>
+        <v>15.696999999999999</v>
       </c>
       <c r="E5" t="s">
         <v>60</v>
@@ -774,7 +789,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="6" spans="1:6">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>10</v>
       </c>
@@ -785,7 +800,7 @@
         <v>55</v>
       </c>
       <c r="D6">
-        <v>17.124</v>
+        <v>17.605</v>
       </c>
       <c r="E6" t="s">
         <v>61</v>
@@ -794,7 +809,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="7" spans="1:6">
+    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>11</v>
       </c>
@@ -805,7 +820,7 @@
         <v>55</v>
       </c>
       <c r="D7">
-        <v>21.465</v>
+        <v>21.88</v>
       </c>
       <c r="E7" t="s">
         <v>62</v>
@@ -814,7 +829,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="8" spans="1:6">
+    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>12</v>
       </c>
@@ -825,7 +840,7 @@
         <v>55</v>
       </c>
       <c r="D8">
-        <v>23.658</v>
+        <v>23.658000000000001</v>
       </c>
       <c r="E8" t="s">
         <v>63</v>
@@ -834,7 +849,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="9" spans="1:6">
+    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>13</v>
       </c>
@@ -854,7 +869,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="10" spans="1:6">
+    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>14</v>
       </c>
@@ -874,7 +889,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="11" spans="1:6">
+    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>15</v>
       </c>
@@ -894,7 +909,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="12" spans="1:6">
+    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>16</v>
       </c>
@@ -905,7 +920,7 @@
         <v>55</v>
       </c>
       <c r="D12">
-        <v>10.646</v>
+        <v>10.646000000000001</v>
       </c>
       <c r="E12" t="s">
         <v>67</v>
@@ -914,7 +929,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="13" spans="1:6">
+    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>17</v>
       </c>
@@ -934,7 +949,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="14" spans="1:6">
+    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>18</v>
       </c>
@@ -954,7 +969,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="15" spans="1:6">
+    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>19</v>
       </c>
@@ -965,7 +980,7 @@
         <v>55</v>
       </c>
       <c r="D15">
-        <v>17.504</v>
+        <v>17.504000000000001</v>
       </c>
       <c r="E15" t="s">
         <v>70</v>
@@ -974,7 +989,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="16" spans="1:6">
+    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>20</v>
       </c>
@@ -994,7 +1009,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="17" spans="1:6">
+    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>21</v>
       </c>
@@ -1005,7 +1020,7 @@
         <v>54</v>
       </c>
       <c r="D17">
-        <v>17.328</v>
+        <v>17.327999999999999</v>
       </c>
       <c r="E17" t="s">
         <v>72</v>
@@ -1014,7 +1029,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="18" spans="1:6">
+    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>22</v>
       </c>
@@ -1034,7 +1049,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="19" spans="1:6">
+    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>23</v>
       </c>
@@ -1045,7 +1060,7 @@
         <v>54</v>
       </c>
       <c r="D19">
-        <v>7.174</v>
+        <v>7.1740000000000004</v>
       </c>
       <c r="E19" t="s">
         <v>74</v>
@@ -1054,7 +1069,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="20" spans="1:6">
+    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>24</v>
       </c>
@@ -1074,7 +1089,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="21" spans="1:6">
+    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>25</v>
       </c>
@@ -1094,7 +1109,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="22" spans="1:6">
+    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>26</v>
       </c>
@@ -1105,7 +1120,7 @@
         <v>56</v>
       </c>
       <c r="D22">
-        <v>16.079</v>
+        <v>15.65</v>
       </c>
       <c r="E22" t="s">
         <v>77</v>
@@ -1114,7 +1129,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="23" spans="1:6">
+    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>27</v>
       </c>
@@ -1125,7 +1140,7 @@
         <v>56</v>
       </c>
       <c r="D23">
-        <v>16.889</v>
+        <v>16.888999999999999</v>
       </c>
       <c r="E23" t="s">
         <v>78</v>
@@ -1134,7 +1149,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="24" spans="1:6">
+    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>28</v>
       </c>
@@ -1154,7 +1169,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="25" spans="1:6">
+    <row r="25" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>29</v>
       </c>
@@ -1165,7 +1180,7 @@
         <v>56</v>
       </c>
       <c r="D25">
-        <v>19.15</v>
+        <v>19.149999999999999</v>
       </c>
       <c r="E25" t="s">
         <v>80</v>
@@ -1174,7 +1189,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="26" spans="1:6">
+    <row r="26" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>30</v>
       </c>
@@ -1185,7 +1200,7 @@
         <v>56</v>
       </c>
       <c r="D26">
-        <v>18.325</v>
+        <v>18.324999999999999</v>
       </c>
       <c r="E26" t="s">
         <v>81</v>
@@ -1194,7 +1209,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="27" spans="1:6">
+    <row r="27" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>31</v>
       </c>
@@ -1214,7 +1229,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="28" spans="1:6">
+    <row r="28" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>32</v>
       </c>
@@ -1225,7 +1240,7 @@
         <v>56</v>
       </c>
       <c r="D28">
-        <v>8.904</v>
+        <v>8.9039999999999999</v>
       </c>
       <c r="E28" t="s">
         <v>83</v>
@@ -1234,7 +1249,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="29" spans="1:6">
+    <row r="29" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>33</v>
       </c>
@@ -1245,7 +1260,7 @@
         <v>56</v>
       </c>
       <c r="D29">
-        <v>21.858</v>
+        <v>21.884</v>
       </c>
       <c r="E29" t="s">
         <v>84</v>
@@ -1254,7 +1269,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="30" spans="1:6">
+    <row r="30" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
         <v>34</v>
       </c>
@@ -1265,7 +1280,7 @@
         <v>56</v>
       </c>
       <c r="D30">
-        <v>23.162</v>
+        <v>23.161999999999999</v>
       </c>
       <c r="E30" t="s">
         <v>85</v>
@@ -1274,7 +1289,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="31" spans="1:6">
+    <row r="31" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
         <v>35</v>
       </c>
@@ -1285,7 +1300,7 @@
         <v>56</v>
       </c>
       <c r="D31">
-        <v>24.107</v>
+        <v>24.106999999999999</v>
       </c>
       <c r="E31" t="s">
         <v>86</v>
@@ -1294,7 +1309,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="32" spans="1:6">
+    <row r="32" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
         <v>36</v>
       </c>
@@ -1305,7 +1320,7 @@
         <v>56</v>
       </c>
       <c r="D32">
-        <v>25.193</v>
+        <v>25.193000000000001</v>
       </c>
       <c r="E32" t="s">
         <v>87</v>
@@ -1314,7 +1329,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="33" spans="1:6">
+    <row r="33" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
         <v>37</v>
       </c>
@@ -1325,7 +1340,7 @@
         <v>56</v>
       </c>
       <c r="D33">
-        <v>24.804</v>
+        <v>24.803999999999998</v>
       </c>
       <c r="E33" t="s">
         <v>88</v>
@@ -1334,7 +1349,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="34" spans="1:6">
+    <row r="34" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
         <v>38</v>
       </c>
@@ -1345,7 +1360,7 @@
         <v>56</v>
       </c>
       <c r="D34">
-        <v>23.147</v>
+        <v>23.146999999999998</v>
       </c>
       <c r="E34" t="s">
         <v>89</v>
@@ -1354,7 +1369,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="35" spans="1:6">
+    <row r="35" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
         <v>39</v>
       </c>
@@ -1365,7 +1380,7 @@
         <v>56</v>
       </c>
       <c r="D35">
-        <v>14.065</v>
+        <v>14.959</v>
       </c>
       <c r="E35" t="s">
         <v>90</v>
@@ -1374,7 +1389,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="36" spans="1:6">
+    <row r="36" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
         <v>40</v>
       </c>
@@ -1385,7 +1400,7 @@
         <v>56</v>
       </c>
       <c r="D36">
-        <v>4.195</v>
+        <v>4.1950000000000003</v>
       </c>
       <c r="E36" t="s">
         <v>91</v>
@@ -1394,7 +1409,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="37" spans="1:6">
+    <row r="37" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
         <v>41</v>
       </c>
@@ -1405,7 +1420,7 @@
         <v>56</v>
       </c>
       <c r="D37">
-        <v>8.738</v>
+        <v>8.7379999999999995</v>
       </c>
       <c r="E37" t="s">
         <v>92</v>
@@ -1414,7 +1429,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="38" spans="1:6">
+    <row r="38" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
         <v>42</v>
       </c>
@@ -1425,7 +1440,7 @@
         <v>56</v>
       </c>
       <c r="D38">
-        <v>25.047</v>
+        <v>25.047000000000001</v>
       </c>
       <c r="E38" t="s">
         <v>93</v>
@@ -1434,7 +1449,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="39" spans="1:6">
+    <row r="39" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
         <v>43</v>
       </c>
@@ -1445,7 +1460,7 @@
         <v>56</v>
       </c>
       <c r="D39">
-        <v>21.138</v>
+        <v>21.138000000000002</v>
       </c>
       <c r="E39" t="s">
         <v>94</v>
@@ -1454,7 +1469,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="40" spans="1:6">
+    <row r="40" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
         <v>44</v>
       </c>
@@ -1465,7 +1480,7 @@
         <v>56</v>
       </c>
       <c r="D40">
-        <v>24.543</v>
+        <v>24.542999999999999</v>
       </c>
       <c r="E40" t="s">
         <v>95</v>
@@ -1474,7 +1489,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="41" spans="1:6">
+    <row r="41" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
         <v>45</v>
       </c>
@@ -1485,7 +1500,7 @@
         <v>56</v>
       </c>
       <c r="D41">
-        <v>12.601</v>
+        <v>12.601000000000001</v>
       </c>
       <c r="E41" t="s">
         <v>96</v>
@@ -1494,7 +1509,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="42" spans="1:6">
+    <row r="42" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
         <v>46</v>
       </c>
@@ -1505,7 +1520,7 @@
         <v>54</v>
       </c>
       <c r="D42">
-        <v>9.779999999999999</v>
+        <v>9.7799999999999994</v>
       </c>
       <c r="E42" t="s">
         <v>97</v>
@@ -1514,7 +1529,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="43" spans="1:6">
+    <row r="43" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
         <v>47</v>
       </c>

--- a/data/field_polygons.xlsx
+++ b/data/field_polygons.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F43"/>
+  <dimension ref="A1:F44"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -477,11 +477,11 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>19.686</v>
+        <v>21.22</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>{"type": "FeatureCollection", "features": [{"type": "Feature", "properties": {}, "geometry": {"type": "Polygon", "coordinates": [[[34.122151, -12.514203], [34.121969, -12.51435], [34.121486, -12.514873], [34.12095, -12.515491], [34.120113, -12.516423], [34.119469, -12.517156], [34.119147, -12.517533], [34.118975, -12.517805], [34.119523, -12.518758], [34.12037, -12.520056], [34.123503, -12.518433], [34.123385, -12.518245], [34.123889, -12.517973], [34.124061, -12.518224], [34.124662, -12.517889], [34.122151, -12.514203]]]}}]}</t>
+          <t>{"type": "FeatureCollection", "features": [{"type": "Feature", "properties": {}, "geometry": {"type": "Polygon", "coordinates": [[[34.122151, -12.514203], [34.121969, -12.51435], [34.121486, -12.514873], [34.12095, -12.515491], [34.120113, -12.516423], [34.119469, -12.517156], [34.119147, -12.517533], [34.118975, -12.517805], [34.11963, -12.518809], [34.120038, -12.5195], [34.120402, -12.520045], [34.123503, -12.518433], [34.123385, -12.518245], [34.123889, -12.517973], [34.124061, -12.518224], [34.124662, -12.517889], [34.122151, -12.514203]]]}}]}</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -1717,6 +1717,36 @@
       <c r="F43" t="inlineStr">
         <is>
           <t>Low</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>LP10003</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>N41</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>Loam</t>
+        </is>
+      </c>
+      <c r="D44" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>{"type": "FeatureCollection", "features": [{"type": "Feature", "properties": {}, "geometry": {"type": "Polygon", "coordinates": [[[34.151173, -12.583748], [34.151655, -12.584366], [34.152091, -12.584937], [34.152836, -12.585874], [34.15319, -12.585623], [34.152803, -12.585078], [34.152331, -12.58457], [34.152004, -12.584157], [34.151731, -12.583821], [34.151489, -12.583518], [34.151173, -12.583748]]]}}]}</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>Critical</t>
         </is>
       </c>
     </row>

--- a/data/field_polygons.xlsx
+++ b/data/field_polygons.xlsx
@@ -1746,7 +1746,7 @@
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Critical</t>
+          <t>Low</t>
         </is>
       </c>
     </row>

--- a/data/field_polygons.xlsx
+++ b/data/field_polygons.xlsx
@@ -486,7 +486,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Critical</t>
         </is>
       </c>
     </row>
@@ -516,7 +516,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Critical</t>
         </is>
       </c>
     </row>
@@ -546,7 +546,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Critical</t>
         </is>
       </c>
     </row>
@@ -576,7 +576,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Critical</t>
         </is>
       </c>
     </row>
@@ -606,7 +606,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Critical</t>
         </is>
       </c>
     </row>
@@ -636,7 +636,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Critical</t>
         </is>
       </c>
     </row>
@@ -666,7 +666,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Critical</t>
         </is>
       </c>
     </row>
@@ -696,7 +696,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Critical</t>
         </is>
       </c>
     </row>
@@ -726,7 +726,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Critical</t>
         </is>
       </c>
     </row>
@@ -756,7 +756,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Critical</t>
         </is>
       </c>
     </row>
@@ -786,7 +786,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Critical</t>
         </is>
       </c>
     </row>
@@ -816,7 +816,7 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Critical</t>
         </is>
       </c>
     </row>
@@ -846,7 +846,7 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Critical</t>
         </is>
       </c>
     </row>
@@ -876,7 +876,7 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Critical</t>
         </is>
       </c>
     </row>
@@ -906,7 +906,7 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Critical</t>
         </is>
       </c>
     </row>
@@ -936,7 +936,7 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Critical</t>
         </is>
       </c>
     </row>
@@ -966,7 +966,7 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Critical</t>
         </is>
       </c>
     </row>
@@ -996,7 +996,7 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Critical</t>
         </is>
       </c>
     </row>
@@ -1026,7 +1026,7 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Critical</t>
         </is>
       </c>
     </row>
@@ -1056,7 +1056,7 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Critical</t>
         </is>
       </c>
     </row>
@@ -1086,7 +1086,7 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Critical</t>
         </is>
       </c>
     </row>
@@ -1116,7 +1116,7 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Critical</t>
         </is>
       </c>
     </row>
@@ -1146,7 +1146,7 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Critical</t>
         </is>
       </c>
     </row>
@@ -1176,7 +1176,7 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Critical</t>
         </is>
       </c>
     </row>
@@ -1206,7 +1206,7 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Critical</t>
         </is>
       </c>
     </row>
@@ -1236,7 +1236,7 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Critical</t>
         </is>
       </c>
     </row>
@@ -1266,7 +1266,7 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Critical</t>
         </is>
       </c>
     </row>
@@ -1296,7 +1296,7 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Critical</t>
         </is>
       </c>
     </row>
@@ -1326,7 +1326,7 @@
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Critical</t>
         </is>
       </c>
     </row>
@@ -1356,7 +1356,7 @@
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Critical</t>
         </is>
       </c>
     </row>
@@ -1386,7 +1386,7 @@
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Critical</t>
         </is>
       </c>
     </row>
@@ -1416,7 +1416,7 @@
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Critical</t>
         </is>
       </c>
     </row>
@@ -1446,7 +1446,7 @@
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Critical</t>
         </is>
       </c>
     </row>
@@ -1476,7 +1476,7 @@
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Critical</t>
         </is>
       </c>
     </row>
@@ -1506,7 +1506,7 @@
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Critical</t>
         </is>
       </c>
     </row>
@@ -1536,7 +1536,7 @@
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Critical</t>
         </is>
       </c>
     </row>
@@ -1566,7 +1566,7 @@
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Critical</t>
         </is>
       </c>
     </row>
@@ -1596,7 +1596,7 @@
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Critical</t>
         </is>
       </c>
     </row>
@@ -1626,7 +1626,7 @@
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Critical</t>
         </is>
       </c>
     </row>
@@ -1656,7 +1656,7 @@
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Critical</t>
         </is>
       </c>
     </row>
@@ -1686,7 +1686,7 @@
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Critical</t>
         </is>
       </c>
     </row>
@@ -1716,7 +1716,7 @@
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Critical</t>
         </is>
       </c>
     </row>
@@ -1746,7 +1746,7 @@
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Critical</t>
         </is>
       </c>
     </row>

--- a/data/field_polygons.xlsx
+++ b/data/field_polygons.xlsx
@@ -1506,7 +1506,7 @@
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Critical</t>
+          <t>Low</t>
         </is>
       </c>
     </row>

--- a/data/field_polygons.xlsx
+++ b/data/field_polygons.xlsx
@@ -666,7 +666,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Critical</t>
+          <t>Moderate</t>
         </is>
       </c>
     </row>
@@ -936,7 +936,7 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Critical</t>
+          <t>Moderate</t>
         </is>
       </c>
     </row>
@@ -966,7 +966,7 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Critical</t>
+          <t>Low</t>
         </is>
       </c>
     </row>

--- a/data/field_polygons.xlsx
+++ b/data/field_polygons.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="10695" windowHeight="7290"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="20490" windowHeight="7320"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>

--- a/data/field_polygons.xlsx
+++ b/data/field_polygons.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="221" uniqueCount="104">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="223" uniqueCount="106">
   <si>
     <t>Field</t>
   </si>
@@ -331,6 +331,12 @@
   </si>
   <si>
     <t>{"type": "FeatureCollection", "features": [{"type": "Feature", "properties": {}, "geometry": {"type": "Polygon", "coordinates": [[[34.151173, -12.583748], [34.151655, -12.584366], [34.152091, -12.584937], [34.152836, -12.585874], [34.15319, -12.585623], [34.152803, -12.585078], [34.152331, -12.58457], [34.152004, -12.584157], [34.151731, -12.583821], [34.151489, -12.583518], [34.151173, -12.583748]]]}}]}</t>
+  </si>
+  <si>
+    <t>Survey Date</t>
+  </si>
+  <si>
+    <t>Surveyor</t>
   </si>
 </sst>
 </file>
@@ -693,10 +699,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F44"/>
+  <dimension ref="A1:H44"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="6" max="6" width="11.42578125" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -715,8 +724,14 @@
       <c r="F1" s="1" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G1" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>6</v>
       </c>
@@ -736,7 +751,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>11</v>
       </c>
@@ -756,7 +771,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>15</v>
       </c>
@@ -776,7 +791,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>18</v>
       </c>
@@ -796,7 +811,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>20</v>
       </c>
@@ -816,7 +831,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>22</v>
       </c>
@@ -836,7 +851,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>25</v>
       </c>
@@ -856,7 +871,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>28</v>
       </c>
@@ -876,7 +891,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>30</v>
       </c>
@@ -896,7 +911,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>32</v>
       </c>
@@ -916,7 +931,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>34</v>
       </c>
@@ -936,7 +951,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>37</v>
       </c>
@@ -956,7 +971,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>39</v>
       </c>
@@ -976,7 +991,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>41</v>
       </c>
@@ -996,7 +1011,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>43</v>
       </c>

--- a/data/field_polygons.xlsx
+++ b/data/field_polygons.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="20490" windowHeight="7320"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="10695" windowHeight="7290"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -39,6 +39,12 @@
     <t>Stress Level</t>
   </si>
   <si>
+    <t>Survey Date</t>
+  </si>
+  <si>
+    <t>Surveyor</t>
+  </si>
+  <si>
     <t>DG01000</t>
   </si>
   <si>
@@ -331,12 +337,6 @@
   </si>
   <si>
     <t>{"type": "FeatureCollection", "features": [{"type": "Feature", "properties": {}, "geometry": {"type": "Polygon", "coordinates": [[[34.151173, -12.583748], [34.151655, -12.584366], [34.152091, -12.584937], [34.152836, -12.585874], [34.15319, -12.585623], [34.152803, -12.585078], [34.152331, -12.58457], [34.152004, -12.584157], [34.151731, -12.583821], [34.151489, -12.583518], [34.151173, -12.583748]]]}}]}</t>
-  </si>
-  <si>
-    <t>Survey Date</t>
-  </si>
-  <si>
-    <t>Surveyor</t>
   </si>
 </sst>
 </file>
@@ -702,7 +702,7 @@
   <dimension ref="A1:H44"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="6" max="6" width="11.42578125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="15.5703125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -725,870 +725,870 @@
         <v>5</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>104</v>
+        <v>6</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>105</v>
+        <v>7</v>
       </c>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="B2" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="C2" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="D2">
         <v>21.22</v>
       </c>
       <c r="E2" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="F2" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="B3" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="C3" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="D3">
         <v>9.1349999999999998</v>
       </c>
       <c r="E3" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="F3" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
+        <v>17</v>
+      </c>
+      <c r="B4" t="s">
+        <v>18</v>
+      </c>
+      <c r="C4" t="s">
         <v>15</v>
-      </c>
-      <c r="B4" t="s">
-        <v>16</v>
-      </c>
-      <c r="C4" t="s">
-        <v>13</v>
       </c>
       <c r="D4">
         <v>16.341999999999999</v>
       </c>
       <c r="E4" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="F4" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="B5" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="C5" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="D5">
         <v>15.696999999999999</v>
       </c>
       <c r="E5" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="F5" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="B6" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="C6" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="D6">
         <v>17.605</v>
       </c>
       <c r="E6" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="F6" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="B7" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="C7" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="D7">
         <v>21.88</v>
       </c>
       <c r="E7" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="F7" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="B8" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="C8" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="D8">
         <v>23.658000000000001</v>
       </c>
       <c r="E8" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="F8" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="B9" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="C9" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="D9">
         <v>14.504</v>
       </c>
       <c r="E9" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="F9" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="B10" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="C10" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="D10">
         <v>31.628</v>
       </c>
       <c r="E10" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="F10" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="B11" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="C11" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="D11">
         <v>3.024</v>
       </c>
       <c r="E11" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="F11" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="B12" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="C12" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="D12">
         <v>10.646000000000001</v>
       </c>
       <c r="E12" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="F12" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
+        <v>39</v>
+      </c>
+      <c r="B13" t="s">
         <v>37</v>
       </c>
-      <c r="B13" t="s">
-        <v>35</v>
-      </c>
       <c r="C13" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="D13">
         <v>31.387</v>
       </c>
       <c r="E13" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="F13" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="B14" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="C14" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="D14">
         <v>14.202</v>
       </c>
       <c r="E14" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="F14" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="B15" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="C15" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="D15">
         <v>17.504000000000001</v>
       </c>
       <c r="E15" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="F15" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="B16" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="C16" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="D16">
         <v>18.895</v>
       </c>
       <c r="E16" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="F16" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="B17" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="C17" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="D17">
         <v>17.327999999999999</v>
       </c>
       <c r="E17" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="F17" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="B18" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="C18" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="D18">
         <v>11.3</v>
       </c>
       <c r="E18" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="F18" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="B19" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="C19" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="D19">
         <v>7.1740000000000004</v>
       </c>
       <c r="E19" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="F19" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="B20" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="C20" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="D20">
         <v>10.439</v>
       </c>
       <c r="E20" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="F20" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="B21" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="C21" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="D21">
         <v>25.122</v>
       </c>
       <c r="E21" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="F21" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="B22" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="C22" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="D22">
         <v>15.65</v>
       </c>
       <c r="E22" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="F22" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="B23" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="C23" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="D23">
         <v>16.888999999999999</v>
       </c>
       <c r="E23" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="F23" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="B24" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="C24" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="D24">
         <v>18.552</v>
       </c>
       <c r="E24" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="F24" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="B25" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="C25" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="D25">
         <v>19.149999999999999</v>
       </c>
       <c r="E25" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="F25" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="B26" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="C26" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="D26">
         <v>18.324999999999999</v>
       </c>
       <c r="E26" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="F26" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="B27" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="C27" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="D27">
         <v>13.993</v>
       </c>
       <c r="E27" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="F27" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="B28" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="C28" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="D28">
         <v>8.9039999999999999</v>
       </c>
       <c r="E28" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="F28" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="B29" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="C29" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="D29">
         <v>21.884</v>
       </c>
       <c r="E29" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="F29" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="B30" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="C30" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="D30">
         <v>23.161999999999999</v>
       </c>
       <c r="E30" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="F30" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="B31" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="C31" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="D31">
         <v>24.106999999999999</v>
       </c>
       <c r="E31" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="F31" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="B32" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="C32" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="D32">
         <v>25.193000000000001</v>
       </c>
       <c r="E32" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="F32" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
     </row>
     <row r="33" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="B33" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="C33" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="D33">
         <v>24.803999999999998</v>
       </c>
       <c r="E33" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="F33" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
     </row>
     <row r="34" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="B34" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="C34" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="D34">
         <v>23.146999999999998</v>
       </c>
       <c r="E34" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="F34" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
     </row>
     <row r="35" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="B35" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="C35" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="D35">
         <v>14.959</v>
       </c>
       <c r="E35" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="F35" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
     </row>
     <row r="36" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="B36" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="C36" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="D36">
         <v>4.1950000000000003</v>
       </c>
       <c r="E36" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="F36" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
     </row>
     <row r="37" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="B37" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="C37" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="D37">
         <v>8.7379999999999995</v>
       </c>
       <c r="E37" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="F37" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
     </row>
     <row r="38" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="B38" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="C38" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="D38">
         <v>25.047000000000001</v>
       </c>
       <c r="E38" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="F38" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
     </row>
     <row r="39" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="B39" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="C39" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="D39">
         <v>21.138000000000002</v>
       </c>
       <c r="E39" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="F39" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
     </row>
     <row r="40" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="B40" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="C40" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="D40">
         <v>24.542999999999999</v>
       </c>
       <c r="E40" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="F40" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
     </row>
     <row r="41" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="B41" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="C41" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="D41">
         <v>12.601000000000001</v>
       </c>
       <c r="E41" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="F41" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
     </row>
     <row r="42" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="B42" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="C42" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="D42">
         <v>9.7799999999999994</v>
       </c>
       <c r="E42" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="F42" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
     </row>
     <row r="43" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="B43" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="C43" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="D43">
         <v>11.125</v>
       </c>
       <c r="E43" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="F43" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
     </row>
     <row r="44" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="B44" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="C44" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="D44">
         <v>1.46</v>
       </c>
       <c r="E44" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="F44" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
     </row>
   </sheetData>
